--- a/artfynd/A 49122-2025 artfynd.xlsx
+++ b/artfynd/A 49122-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3286,6 +3286,4127 @@
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>129417966</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79660</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Frönberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>367358</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6872812</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129418000</v>
+      </c>
+      <c r="B22" t="n">
+        <v>92822</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Frönberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>367377</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6872921</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129417970</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79631</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Frönberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>367279</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6872915</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129417977</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57831</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Frönberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>367390</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6872907</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129417986</v>
+      </c>
+      <c r="B25" t="n">
+        <v>92822</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Frönberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>367310</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6872693</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>129417975</v>
+      </c>
+      <c r="B26" t="n">
+        <v>92826</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Frönberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>367263</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6872692</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>129417988</v>
+      </c>
+      <c r="B27" t="n">
+        <v>92822</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Frönberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>367381</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6872742</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>129417983</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Frönberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>367341</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6872850</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129417982</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Frönberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>367313</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6872755</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>129417981</v>
+      </c>
+      <c r="B30" t="n">
+        <v>91713</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Frönberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>367358</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6872748</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>129417965</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79660</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Frönberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>367465</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6872703</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>129417985</v>
+      </c>
+      <c r="B32" t="n">
+        <v>92822</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Frönberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>367272</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6872689</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>129417987</v>
+      </c>
+      <c r="B33" t="n">
+        <v>92822</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Frönberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>367319</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6872675</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>129417967</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79660</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Frönberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>367314</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6872919</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>129417992</v>
+      </c>
+      <c r="B35" t="n">
+        <v>92822</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Frönberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>367466</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6872692</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>129417980</v>
+      </c>
+      <c r="B36" t="n">
+        <v>91554</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Frönberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>367486</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6872703</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>129417978</v>
+      </c>
+      <c r="B37" t="n">
+        <v>78798</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Frönberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>367466</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6872704</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>129417976</v>
+      </c>
+      <c r="B38" t="n">
+        <v>5493</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>101410</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Reliktbock</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Nothorhina muricata</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Frönberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>367265</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6872697</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>129417993</v>
+      </c>
+      <c r="B39" t="n">
+        <v>92822</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Frönberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>367508</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6872697</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>129417996</v>
+      </c>
+      <c r="B40" t="n">
+        <v>92822</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Frönberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>367487</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6872708</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>129417984</v>
+      </c>
+      <c r="B41" t="n">
+        <v>92822</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Frönberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>367266</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6872707</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>129417964</v>
+      </c>
+      <c r="B42" t="n">
+        <v>79073</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>185</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Frönberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>367309</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6872933</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>129417995</v>
+      </c>
+      <c r="B43" t="n">
+        <v>92822</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Frönberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>367532</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6872711</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>129417969</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79631</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Frönberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>367342</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6872834</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>129417989</v>
+      </c>
+      <c r="B45" t="n">
+        <v>92822</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Frönberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>367400</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6872675</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>129417997</v>
+      </c>
+      <c r="B46" t="n">
+        <v>92822</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Frönberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>367429</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6872754</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>129417991</v>
+      </c>
+      <c r="B47" t="n">
+        <v>92822</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Frönberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>367457</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6872685</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>129417999</v>
+      </c>
+      <c r="B48" t="n">
+        <v>92822</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Frönberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>367326</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6872818</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>129418002</v>
+      </c>
+      <c r="B49" t="n">
+        <v>92816</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Frönberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>367263</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6872692</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>129417971</v>
+      </c>
+      <c r="B50" t="n">
+        <v>90572</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Frönberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>367385</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6872892</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>129417998</v>
+      </c>
+      <c r="B51" t="n">
+        <v>92822</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Frönberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>367408</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6872746</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>129418003</v>
+      </c>
+      <c r="B52" t="n">
+        <v>78444</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Frönberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>367471</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6872690</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>129417990</v>
+      </c>
+      <c r="B53" t="n">
+        <v>92822</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Frönberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>367419</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6872666</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>129418004</v>
+      </c>
+      <c r="B54" t="n">
+        <v>78444</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Frönberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>367380</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6872914</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>129417994</v>
+      </c>
+      <c r="B55" t="n">
+        <v>92822</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Frönberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>367525</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6872692</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>129417968</v>
+      </c>
+      <c r="B56" t="n">
+        <v>79631</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Frönberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>367311</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6872696</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>129417972</v>
+      </c>
+      <c r="B57" t="n">
+        <v>57887</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Frönberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>367434</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6872745</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>129418001</v>
+      </c>
+      <c r="B58" t="n">
+        <v>78049</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Frönberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>367471</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6872691</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 49122-2025 artfynd.xlsx
+++ b/artfynd/A 49122-2025 artfynd.xlsx
@@ -3288,32 +3288,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129417966</v>
+        <v>129418000</v>
       </c>
       <c r="B21" t="n">
-        <v>79660</v>
+        <v>92825</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3323,10 +3323,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>367358</v>
+        <v>367377</v>
       </c>
       <c r="R21" t="n">
-        <v>6872812</v>
+        <v>6872921</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3395,32 +3395,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129418000</v>
+        <v>129417966</v>
       </c>
       <c r="B22" t="n">
-        <v>92822</v>
+        <v>79662</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3430,10 +3430,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>367377</v>
+        <v>367358</v>
       </c>
       <c r="R22" t="n">
-        <v>6872921</v>
+        <v>6872812</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3505,7 +3505,7 @@
         <v>129417970</v>
       </c>
       <c r="B23" t="n">
-        <v>79631</v>
+        <v>79633</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3609,57 +3609,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129417977</v>
+        <v>129417983</v>
       </c>
       <c r="B24" t="n">
-        <v>57831</v>
+        <v>79043</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Frönberget, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>367390</v>
+        <v>367341</v>
       </c>
       <c r="R24" t="n">
-        <v>6872907</v>
+        <v>6872850</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3691,7 +3679,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3701,7 +3689,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3710,8 +3698,24 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3728,10 +3732,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129417986</v>
+        <v>129417988</v>
       </c>
       <c r="B25" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3763,10 +3767,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>367310</v>
+        <v>367381</v>
       </c>
       <c r="R25" t="n">
-        <v>6872693</v>
+        <v>6872742</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3798,7 +3802,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3808,7 +3812,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3838,7 +3842,7 @@
         <v>129417975</v>
       </c>
       <c r="B26" t="n">
-        <v>92826</v>
+        <v>92829</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3942,10 +3946,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129417988</v>
+        <v>129417986</v>
       </c>
       <c r="B27" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3977,10 +3981,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>367381</v>
+        <v>367310</v>
       </c>
       <c r="R27" t="n">
-        <v>6872742</v>
+        <v>6872693</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4012,7 +4016,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4022,7 +4026,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4049,45 +4053,57 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129417983</v>
+        <v>129417977</v>
       </c>
       <c r="B28" t="n">
-        <v>79041</v>
+        <v>57831</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Frönberget, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>367341</v>
+        <v>367390</v>
       </c>
       <c r="R28" t="n">
-        <v>6872850</v>
+        <v>6872907</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4119,7 +4135,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4129,7 +4145,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4138,24 +4154,8 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -4175,7 +4175,7 @@
         <v>129417982</v>
       </c>
       <c r="B29" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4298,32 +4298,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129417981</v>
+        <v>129417965</v>
       </c>
       <c r="B30" t="n">
-        <v>91713</v>
+        <v>79662</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4333,10 +4333,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>367358</v>
+        <v>367465</v>
       </c>
       <c r="R30" t="n">
-        <v>6872748</v>
+        <v>6872703</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4368,7 +4368,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4405,32 +4405,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129417965</v>
+        <v>129417981</v>
       </c>
       <c r="B31" t="n">
-        <v>79660</v>
+        <v>91716</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>1503</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4440,10 +4440,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>367465</v>
+        <v>367358</v>
       </c>
       <c r="R31" t="n">
-        <v>6872703</v>
+        <v>6872748</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4515,7 +4515,7 @@
         <v>129417985</v>
       </c>
       <c r="B32" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4622,7 +4622,7 @@
         <v>129417987</v>
       </c>
       <c r="B33" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4729,7 +4729,7 @@
         <v>129417967</v>
       </c>
       <c r="B34" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4833,32 +4833,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129417992</v>
+        <v>129417980</v>
       </c>
       <c r="B35" t="n">
-        <v>92822</v>
+        <v>91557</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>1204</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4868,10 +4868,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>367466</v>
+        <v>367486</v>
       </c>
       <c r="R35" t="n">
-        <v>6872692</v>
+        <v>6872703</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4913,7 +4913,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4940,32 +4940,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129417980</v>
+        <v>129417992</v>
       </c>
       <c r="B36" t="n">
-        <v>91554</v>
+        <v>92825</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1204</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4975,10 +4975,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>367486</v>
+        <v>367466</v>
       </c>
       <c r="R36" t="n">
-        <v>6872703</v>
+        <v>6872692</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5010,7 +5010,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5020,7 +5020,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5050,7 +5050,7 @@
         <v>129417978</v>
       </c>
       <c r="B37" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5261,10 +5261,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129417993</v>
+        <v>129417984</v>
       </c>
       <c r="B39" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5296,10 +5296,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>367508</v>
+        <v>367266</v>
       </c>
       <c r="R39" t="n">
-        <v>6872697</v>
+        <v>6872707</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5331,7 +5331,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5341,7 +5341,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5371,7 +5371,7 @@
         <v>129417996</v>
       </c>
       <c r="B40" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5475,10 +5475,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129417984</v>
+        <v>129417993</v>
       </c>
       <c r="B41" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5510,10 +5510,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>367266</v>
+        <v>367508</v>
       </c>
       <c r="R41" t="n">
-        <v>6872707</v>
+        <v>6872697</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5545,7 +5545,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5585,7 +5585,7 @@
         <v>129417964</v>
       </c>
       <c r="B42" t="n">
-        <v>79073</v>
+        <v>79075</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         <v>129417995</v>
       </c>
       <c r="B43" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5799,7 +5799,7 @@
         <v>129417969</v>
       </c>
       <c r="B44" t="n">
-        <v>79631</v>
+        <v>79633</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5906,7 +5906,7 @@
         <v>129417989</v>
       </c>
       <c r="B45" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6010,10 +6010,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129417997</v>
+        <v>129417999</v>
       </c>
       <c r="B46" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6045,10 +6045,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>367429</v>
+        <v>367326</v>
       </c>
       <c r="R46" t="n">
-        <v>6872754</v>
+        <v>6872818</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6080,7 +6080,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6090,7 +6090,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6120,7 +6120,7 @@
         <v>129417991</v>
       </c>
       <c r="B47" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6224,10 +6224,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129417999</v>
+        <v>129417997</v>
       </c>
       <c r="B48" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6259,10 +6259,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>367326</v>
+        <v>367429</v>
       </c>
       <c r="R48" t="n">
-        <v>6872818</v>
+        <v>6872754</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6304,7 +6304,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6331,10 +6331,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129418002</v>
+        <v>129417971</v>
       </c>
       <c r="B49" t="n">
-        <v>92816</v>
+        <v>90575</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6342,21 +6342,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4362</v>
+        <v>1962</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6366,10 +6366,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>367263</v>
+        <v>367385</v>
       </c>
       <c r="R49" t="n">
-        <v>6872692</v>
+        <v>6872892</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6401,7 +6401,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6438,32 +6438,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129417971</v>
+        <v>129417998</v>
       </c>
       <c r="B50" t="n">
-        <v>90572</v>
+        <v>92825</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6473,10 +6473,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>367385</v>
+        <v>367408</v>
       </c>
       <c r="R50" t="n">
-        <v>6872892</v>
+        <v>6872746</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6508,7 +6508,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6518,7 +6518,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6545,32 +6545,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129417998</v>
+        <v>129418002</v>
       </c>
       <c r="B51" t="n">
-        <v>92822</v>
+        <v>92819</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6580,10 +6580,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>367408</v>
+        <v>367263</v>
       </c>
       <c r="R51" t="n">
-        <v>6872746</v>
+        <v>6872692</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6615,7 +6615,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6625,7 +6625,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6655,7 +6655,7 @@
         <v>129418003</v>
       </c>
       <c r="B52" t="n">
-        <v>78444</v>
+        <v>78446</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6759,32 +6759,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129417990</v>
+        <v>129418004</v>
       </c>
       <c r="B53" t="n">
-        <v>92822</v>
+        <v>78446</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6794,10 +6794,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>367419</v>
+        <v>367380</v>
       </c>
       <c r="R53" t="n">
-        <v>6872666</v>
+        <v>6872914</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6829,7 +6829,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6839,7 +6839,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6866,32 +6866,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129418004</v>
+        <v>129417990</v>
       </c>
       <c r="B54" t="n">
-        <v>78444</v>
+        <v>92825</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6901,10 +6901,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>367380</v>
+        <v>367419</v>
       </c>
       <c r="R54" t="n">
-        <v>6872914</v>
+        <v>6872666</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6946,7 +6946,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6973,32 +6973,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129417994</v>
+        <v>129417968</v>
       </c>
       <c r="B55" t="n">
-        <v>92822</v>
+        <v>79633</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -7008,10 +7008,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>367525</v>
+        <v>367311</v>
       </c>
       <c r="R55" t="n">
-        <v>6872692</v>
+        <v>6872696</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7053,7 +7053,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7080,32 +7080,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129417968</v>
+        <v>129417994</v>
       </c>
       <c r="B56" t="n">
-        <v>79631</v>
+        <v>92825</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7115,10 +7115,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>367311</v>
+        <v>367525</v>
       </c>
       <c r="R56" t="n">
-        <v>6872696</v>
+        <v>6872692</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7150,7 +7150,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7160,7 +7160,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7187,10 +7187,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129417972</v>
+        <v>129418001</v>
       </c>
       <c r="B57" t="n">
-        <v>57887</v>
+        <v>78051</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7198,42 +7198,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103021</v>
+        <v>6487</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Frönberget, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>367434</v>
+        <v>367471</v>
       </c>
       <c r="R57" t="n">
-        <v>6872745</v>
+        <v>6872691</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7265,7 +7257,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7275,7 +7267,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7302,10 +7294,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129418001</v>
+        <v>129417972</v>
       </c>
       <c r="B58" t="n">
-        <v>78049</v>
+        <v>57887</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7313,34 +7305,42 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6487</v>
+        <v>103021</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Frönberget, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>367471</v>
+        <v>367434</v>
       </c>
       <c r="R58" t="n">
-        <v>6872691</v>
+        <v>6872745</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7372,7 +7372,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7382,7 +7382,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD58" t="b">

--- a/artfynd/A 49122-2025 artfynd.xlsx
+++ b/artfynd/A 49122-2025 artfynd.xlsx
@@ -3291,7 +3291,7 @@
         <v>129418000</v>
       </c>
       <c r="B21" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
         <v>129417966</v>
       </c>
       <c r="B22" t="n">
-        <v>79689</v>
+        <v>79694</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>129417970</v>
       </c>
       <c r="B23" t="n">
-        <v>79660</v>
+        <v>79665</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3609,10 +3609,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129417986</v>
+        <v>129417977</v>
       </c>
       <c r="B24" t="n">
-        <v>92863</v>
+        <v>57839</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3620,34 +3620,46 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>103031</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Frönberget, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>367310</v>
+        <v>367390</v>
       </c>
       <c r="R24" t="n">
-        <v>6872693</v>
+        <v>6872907</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3679,7 +3691,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3689,7 +3701,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3716,32 +3728,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129417975</v>
+        <v>129417986</v>
       </c>
       <c r="B25" t="n">
-        <v>92867</v>
+        <v>92869</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3751,10 +3763,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>367263</v>
+        <v>367310</v>
       </c>
       <c r="R25" t="n">
-        <v>6872692</v>
+        <v>6872693</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3786,7 +3798,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3796,7 +3808,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3823,32 +3835,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129417988</v>
+        <v>129417975</v>
       </c>
       <c r="B26" t="n">
-        <v>92863</v>
+        <v>92873</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3858,10 +3870,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>367381</v>
+        <v>367263</v>
       </c>
       <c r="R26" t="n">
-        <v>6872742</v>
+        <v>6872692</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3893,7 +3905,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3903,7 +3915,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3930,32 +3942,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129417983</v>
+        <v>129417988</v>
       </c>
       <c r="B27" t="n">
-        <v>79070</v>
+        <v>92869</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3965,10 +3977,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>367341</v>
+        <v>367381</v>
       </c>
       <c r="R27" t="n">
-        <v>6872850</v>
+        <v>6872742</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4000,7 +4012,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4010,7 +4022,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4019,24 +4031,8 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -4053,57 +4049,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129417977</v>
+        <v>129417983</v>
       </c>
       <c r="B28" t="n">
-        <v>57834</v>
+        <v>79075</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Frönberget, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>367390</v>
+        <v>367341</v>
       </c>
       <c r="R28" t="n">
-        <v>6872907</v>
+        <v>6872850</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4135,7 +4119,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4145,7 +4129,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4154,8 +4138,24 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -4175,7 +4175,7 @@
         <v>129417981</v>
       </c>
       <c r="B29" t="n">
-        <v>91754</v>
+        <v>91760</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>129417982</v>
       </c>
       <c r="B30" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4408,7 +4408,7 @@
         <v>129417965</v>
       </c>
       <c r="B31" t="n">
-        <v>79689</v>
+        <v>79694</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
         <v>129417985</v>
       </c>
       <c r="B32" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4622,7 +4622,7 @@
         <v>129417987</v>
       </c>
       <c r="B33" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4729,7 +4729,7 @@
         <v>129417967</v>
       </c>
       <c r="B34" t="n">
-        <v>79689</v>
+        <v>79694</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4836,7 +4836,7 @@
         <v>129417980</v>
       </c>
       <c r="B35" t="n">
-        <v>91595</v>
+        <v>91601</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4943,7 +4943,7 @@
         <v>129417992</v>
       </c>
       <c r="B36" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5047,10 +5047,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129417978</v>
+        <v>129417976</v>
       </c>
       <c r="B37" t="n">
-        <v>78827</v>
+        <v>5493</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5058,21 +5058,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>101410</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>367466</v>
+        <v>367265</v>
       </c>
       <c r="R37" t="n">
-        <v>6872704</v>
+        <v>6872697</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5117,7 +5117,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5127,7 +5127,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5154,10 +5154,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129417976</v>
+        <v>129417978</v>
       </c>
       <c r="B38" t="n">
-        <v>5493</v>
+        <v>78832</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5165,21 +5165,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>101410</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5189,10 +5189,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>367265</v>
+        <v>367466</v>
       </c>
       <c r="R38" t="n">
-        <v>6872697</v>
+        <v>6872704</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5224,7 +5224,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5234,7 +5234,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5264,7 +5264,7 @@
         <v>129417993</v>
       </c>
       <c r="B39" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5371,7 +5371,7 @@
         <v>129417996</v>
       </c>
       <c r="B40" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5478,7 +5478,7 @@
         <v>129417984</v>
       </c>
       <c r="B41" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5585,7 +5585,7 @@
         <v>129417964</v>
       </c>
       <c r="B42" t="n">
-        <v>79102</v>
+        <v>79107</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         <v>129417995</v>
       </c>
       <c r="B43" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5799,7 +5799,7 @@
         <v>129417969</v>
       </c>
       <c r="B44" t="n">
-        <v>79660</v>
+        <v>79665</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5906,7 +5906,7 @@
         <v>129417997</v>
       </c>
       <c r="B45" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>129417991</v>
       </c>
       <c r="B46" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         <v>129417999</v>
       </c>
       <c r="B47" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6227,7 +6227,7 @@
         <v>129417989</v>
       </c>
       <c r="B48" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6334,7 +6334,7 @@
         <v>129417971</v>
       </c>
       <c r="B49" t="n">
-        <v>90613</v>
+        <v>90619</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6441,7 +6441,7 @@
         <v>129418002</v>
       </c>
       <c r="B50" t="n">
-        <v>92857</v>
+        <v>92863</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6548,7 +6548,7 @@
         <v>129417998</v>
       </c>
       <c r="B51" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>129418003</v>
       </c>
       <c r="B52" t="n">
-        <v>78473</v>
+        <v>78478</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6762,7 +6762,7 @@
         <v>129417990</v>
       </c>
       <c r="B53" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6869,7 +6869,7 @@
         <v>129418004</v>
       </c>
       <c r="B54" t="n">
-        <v>78473</v>
+        <v>78478</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6973,32 +6973,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129417968</v>
+        <v>129417994</v>
       </c>
       <c r="B55" t="n">
-        <v>79660</v>
+        <v>92869</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -7008,10 +7008,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>367311</v>
+        <v>367525</v>
       </c>
       <c r="R55" t="n">
-        <v>6872696</v>
+        <v>6872692</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7053,7 +7053,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7080,32 +7080,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129417994</v>
+        <v>129417968</v>
       </c>
       <c r="B56" t="n">
-        <v>92863</v>
+        <v>79665</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7115,10 +7115,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>367525</v>
+        <v>367311</v>
       </c>
       <c r="R56" t="n">
-        <v>6872692</v>
+        <v>6872696</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7150,7 +7150,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7160,7 +7160,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7187,10 +7187,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129417972</v>
+        <v>129418001</v>
       </c>
       <c r="B57" t="n">
-        <v>57890</v>
+        <v>78083</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7198,42 +7198,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103021</v>
+        <v>6487</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Frönberget, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>367434</v>
+        <v>367471</v>
       </c>
       <c r="R57" t="n">
-        <v>6872745</v>
+        <v>6872691</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7265,7 +7257,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7275,7 +7267,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7302,10 +7294,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129418001</v>
+        <v>129417972</v>
       </c>
       <c r="B58" t="n">
-        <v>78078</v>
+        <v>57895</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7313,34 +7305,42 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6487</v>
+        <v>103021</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Frönberget, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>367471</v>
+        <v>367434</v>
       </c>
       <c r="R58" t="n">
-        <v>6872691</v>
+        <v>6872745</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7372,7 +7372,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7382,7 +7382,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD58" t="b">

--- a/artfynd/A 49122-2025 artfynd.xlsx
+++ b/artfynd/A 49122-2025 artfynd.xlsx
@@ -3288,32 +3288,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129418000</v>
+        <v>129417970</v>
       </c>
       <c r="B21" t="n">
-        <v>92869</v>
+        <v>79666</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3323,10 +3323,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>367377</v>
+        <v>367279</v>
       </c>
       <c r="R21" t="n">
-        <v>6872921</v>
+        <v>6872915</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3395,32 +3395,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129417966</v>
+        <v>129418000</v>
       </c>
       <c r="B22" t="n">
-        <v>79694</v>
+        <v>92870</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3430,10 +3430,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>367358</v>
+        <v>367377</v>
       </c>
       <c r="R22" t="n">
-        <v>6872812</v>
+        <v>6872921</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3502,10 +3502,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129417970</v>
+        <v>129417966</v>
       </c>
       <c r="B23" t="n">
-        <v>79665</v>
+        <v>79695</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3513,21 +3513,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3537,10 +3537,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>367279</v>
+        <v>367358</v>
       </c>
       <c r="R23" t="n">
-        <v>6872915</v>
+        <v>6872812</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3572,7 +3572,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3582,7 +3582,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3609,57 +3609,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129417977</v>
+        <v>129417983</v>
       </c>
       <c r="B24" t="n">
-        <v>57839</v>
+        <v>79076</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Frönberget, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>367390</v>
+        <v>367341</v>
       </c>
       <c r="R24" t="n">
-        <v>6872907</v>
+        <v>6872850</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3691,7 +3679,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3701,7 +3689,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3710,8 +3698,24 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3728,10 +3732,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129417986</v>
+        <v>129417977</v>
       </c>
       <c r="B25" t="n">
-        <v>92869</v>
+        <v>57840</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3739,34 +3743,46 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>103031</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Frönberget, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>367310</v>
+        <v>367390</v>
       </c>
       <c r="R25" t="n">
-        <v>6872693</v>
+        <v>6872907</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3798,7 +3814,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3808,7 +3824,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3835,32 +3851,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129417975</v>
+        <v>129417986</v>
       </c>
       <c r="B26" t="n">
-        <v>92873</v>
+        <v>92870</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3870,10 +3886,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>367263</v>
+        <v>367310</v>
       </c>
       <c r="R26" t="n">
-        <v>6872692</v>
+        <v>6872693</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3905,7 +3921,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3915,7 +3931,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3945,7 +3961,7 @@
         <v>129417988</v>
       </c>
       <c r="B27" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4049,32 +4065,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129417983</v>
+        <v>129417975</v>
       </c>
       <c r="B28" t="n">
-        <v>79075</v>
+        <v>92874</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>4365</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -4084,10 +4100,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>367341</v>
+        <v>367263</v>
       </c>
       <c r="R28" t="n">
-        <v>6872850</v>
+        <v>6872692</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4119,7 +4135,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4129,7 +4145,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4138,24 +4154,8 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -4175,7 +4175,7 @@
         <v>129417981</v>
       </c>
       <c r="B29" t="n">
-        <v>91760</v>
+        <v>91761</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>129417982</v>
       </c>
       <c r="B30" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4408,7 +4408,7 @@
         <v>129417965</v>
       </c>
       <c r="B31" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
         <v>129417985</v>
       </c>
       <c r="B32" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4622,7 +4622,7 @@
         <v>129417987</v>
       </c>
       <c r="B33" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4729,7 +4729,7 @@
         <v>129417967</v>
       </c>
       <c r="B34" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4833,32 +4833,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129417980</v>
+        <v>129417992</v>
       </c>
       <c r="B35" t="n">
-        <v>91601</v>
+        <v>92870</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1204</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4868,10 +4868,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>367486</v>
+        <v>367466</v>
       </c>
       <c r="R35" t="n">
-        <v>6872703</v>
+        <v>6872692</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4913,7 +4913,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4940,32 +4940,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129417992</v>
+        <v>129417980</v>
       </c>
       <c r="B36" t="n">
-        <v>92869</v>
+        <v>91602</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>1204</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4975,10 +4975,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>367466</v>
+        <v>367486</v>
       </c>
       <c r="R36" t="n">
-        <v>6872692</v>
+        <v>6872703</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5010,7 +5010,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5020,7 +5020,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5047,10 +5047,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129417976</v>
+        <v>129417978</v>
       </c>
       <c r="B37" t="n">
-        <v>5493</v>
+        <v>78833</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5058,21 +5058,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>101410</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>367265</v>
+        <v>367466</v>
       </c>
       <c r="R37" t="n">
-        <v>6872697</v>
+        <v>6872704</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5117,7 +5117,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5127,7 +5127,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5154,10 +5154,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129417978</v>
+        <v>129417976</v>
       </c>
       <c r="B38" t="n">
-        <v>78832</v>
+        <v>5493</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5165,21 +5165,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>101410</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5189,10 +5189,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>367466</v>
+        <v>367265</v>
       </c>
       <c r="R38" t="n">
-        <v>6872704</v>
+        <v>6872697</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5224,7 +5224,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5234,7 +5234,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5264,7 +5264,7 @@
         <v>129417993</v>
       </c>
       <c r="B39" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5371,7 +5371,7 @@
         <v>129417996</v>
       </c>
       <c r="B40" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5478,7 +5478,7 @@
         <v>129417984</v>
       </c>
       <c r="B41" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5585,7 +5585,7 @@
         <v>129417964</v>
       </c>
       <c r="B42" t="n">
-        <v>79107</v>
+        <v>79108</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         <v>129417995</v>
       </c>
       <c r="B43" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5799,7 +5799,7 @@
         <v>129417969</v>
       </c>
       <c r="B44" t="n">
-        <v>79665</v>
+        <v>79666</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5906,7 +5906,7 @@
         <v>129417997</v>
       </c>
       <c r="B45" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>129417991</v>
       </c>
       <c r="B46" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6117,10 +6117,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129417999</v>
+        <v>129417989</v>
       </c>
       <c r="B47" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6152,10 +6152,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>367326</v>
+        <v>367400</v>
       </c>
       <c r="R47" t="n">
-        <v>6872818</v>
+        <v>6872675</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6197,7 +6197,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6224,10 +6224,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129417989</v>
+        <v>129417999</v>
       </c>
       <c r="B48" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6259,10 +6259,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>367400</v>
+        <v>367326</v>
       </c>
       <c r="R48" t="n">
-        <v>6872675</v>
+        <v>6872818</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6304,7 +6304,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6334,7 +6334,7 @@
         <v>129417971</v>
       </c>
       <c r="B49" t="n">
-        <v>90619</v>
+        <v>90620</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6438,32 +6438,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129418002</v>
+        <v>129417998</v>
       </c>
       <c r="B50" t="n">
-        <v>92863</v>
+        <v>92870</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6473,10 +6473,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>367263</v>
+        <v>367408</v>
       </c>
       <c r="R50" t="n">
-        <v>6872692</v>
+        <v>6872746</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6508,7 +6508,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6518,7 +6518,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6545,32 +6545,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129417998</v>
+        <v>129418002</v>
       </c>
       <c r="B51" t="n">
-        <v>92869</v>
+        <v>92864</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6580,10 +6580,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>367408</v>
+        <v>367263</v>
       </c>
       <c r="R51" t="n">
-        <v>6872746</v>
+        <v>6872692</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6615,7 +6615,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6625,7 +6625,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6655,7 +6655,7 @@
         <v>129418003</v>
       </c>
       <c r="B52" t="n">
-        <v>78478</v>
+        <v>78479</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6762,7 +6762,7 @@
         <v>129417990</v>
       </c>
       <c r="B53" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6869,7 +6869,7 @@
         <v>129418004</v>
       </c>
       <c r="B54" t="n">
-        <v>78478</v>
+        <v>78479</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6973,32 +6973,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129417994</v>
+        <v>129417968</v>
       </c>
       <c r="B55" t="n">
-        <v>92869</v>
+        <v>79666</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -7008,10 +7008,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>367525</v>
+        <v>367311</v>
       </c>
       <c r="R55" t="n">
-        <v>6872692</v>
+        <v>6872696</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7053,7 +7053,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7080,32 +7080,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129417968</v>
+        <v>129417994</v>
       </c>
       <c r="B56" t="n">
-        <v>79665</v>
+        <v>92870</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7115,10 +7115,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>367311</v>
+        <v>367525</v>
       </c>
       <c r="R56" t="n">
-        <v>6872696</v>
+        <v>6872692</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7150,7 +7150,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7160,7 +7160,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7190,7 +7190,7 @@
         <v>129418001</v>
       </c>
       <c r="B57" t="n">
-        <v>78083</v>
+        <v>78084</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7297,7 +7297,7 @@
         <v>129417972</v>
       </c>
       <c r="B58" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 49122-2025 artfynd.xlsx
+++ b/artfynd/A 49122-2025 artfynd.xlsx
@@ -3288,32 +3288,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129417970</v>
+        <v>129418000</v>
       </c>
       <c r="B21" t="n">
-        <v>79666</v>
+        <v>92870</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3323,10 +3323,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>367279</v>
+        <v>367377</v>
       </c>
       <c r="R21" t="n">
-        <v>6872915</v>
+        <v>6872921</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3395,32 +3395,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129418000</v>
+        <v>129417970</v>
       </c>
       <c r="B22" t="n">
-        <v>92870</v>
+        <v>79666</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3430,10 +3430,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>367377</v>
+        <v>367279</v>
       </c>
       <c r="R22" t="n">
-        <v>6872921</v>
+        <v>6872915</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -4512,7 +4512,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129417985</v>
+        <v>129417987</v>
       </c>
       <c r="B32" t="n">
         <v>92870</v>
@@ -4547,10 +4547,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>367272</v>
+        <v>367319</v>
       </c>
       <c r="R32" t="n">
-        <v>6872689</v>
+        <v>6872675</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4582,7 +4582,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4619,7 +4619,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129417987</v>
+        <v>129417985</v>
       </c>
       <c r="B33" t="n">
         <v>92870</v>
@@ -4654,10 +4654,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>367319</v>
+        <v>367272</v>
       </c>
       <c r="R33" t="n">
-        <v>6872675</v>
+        <v>6872689</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4689,7 +4689,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -6759,32 +6759,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129417990</v>
+        <v>129418004</v>
       </c>
       <c r="B53" t="n">
-        <v>92870</v>
+        <v>78479</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6794,10 +6794,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>367419</v>
+        <v>367380</v>
       </c>
       <c r="R53" t="n">
-        <v>6872666</v>
+        <v>6872914</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6829,7 +6829,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6839,7 +6839,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6866,32 +6866,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129418004</v>
+        <v>129417990</v>
       </c>
       <c r="B54" t="n">
-        <v>78479</v>
+        <v>92870</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6901,10 +6901,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>367380</v>
+        <v>367419</v>
       </c>
       <c r="R54" t="n">
-        <v>6872914</v>
+        <v>6872666</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6946,7 +6946,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD54" t="b">

--- a/artfynd/A 49122-2025 artfynd.xlsx
+++ b/artfynd/A 49122-2025 artfynd.xlsx
@@ -3288,32 +3288,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129418000</v>
+        <v>129417970</v>
       </c>
       <c r="B21" t="n">
-        <v>92870</v>
+        <v>79671</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3323,10 +3323,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>367377</v>
+        <v>367279</v>
       </c>
       <c r="R21" t="n">
-        <v>6872921</v>
+        <v>6872915</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3395,32 +3395,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129417970</v>
+        <v>129418000</v>
       </c>
       <c r="B22" t="n">
-        <v>79666</v>
+        <v>92875</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3430,10 +3430,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>367279</v>
+        <v>367377</v>
       </c>
       <c r="R22" t="n">
-        <v>6872915</v>
+        <v>6872921</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3505,7 +3505,7 @@
         <v>129417966</v>
       </c>
       <c r="B23" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3609,45 +3609,57 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129417983</v>
+        <v>129417977</v>
       </c>
       <c r="B24" t="n">
-        <v>79076</v>
+        <v>57840</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Frönberget, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>367341</v>
+        <v>367390</v>
       </c>
       <c r="R24" t="n">
-        <v>6872850</v>
+        <v>6872907</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3679,7 +3691,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3689,7 +3701,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3698,24 +3710,8 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3732,10 +3728,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129417977</v>
+        <v>129417986</v>
       </c>
       <c r="B25" t="n">
-        <v>57840</v>
+        <v>92875</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3743,46 +3739,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103031</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Frönberget, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>367390</v>
+        <v>367310</v>
       </c>
       <c r="R25" t="n">
-        <v>6872907</v>
+        <v>6872693</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3814,7 +3798,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3824,7 +3808,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3851,32 +3835,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129417986</v>
+        <v>129417975</v>
       </c>
       <c r="B26" t="n">
-        <v>92870</v>
+        <v>92879</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3886,10 +3870,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>367310</v>
+        <v>367263</v>
       </c>
       <c r="R26" t="n">
-        <v>6872693</v>
+        <v>6872692</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3921,7 +3905,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3931,7 +3915,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3961,7 +3945,7 @@
         <v>129417988</v>
       </c>
       <c r="B27" t="n">
-        <v>92870</v>
+        <v>92875</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4065,32 +4049,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129417975</v>
+        <v>129417983</v>
       </c>
       <c r="B28" t="n">
-        <v>92874</v>
+        <v>79081</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4365</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -4100,10 +4084,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>367263</v>
+        <v>367341</v>
       </c>
       <c r="R28" t="n">
-        <v>6872692</v>
+        <v>6872850</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4135,7 +4119,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4145,7 +4129,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4154,8 +4138,24 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -4175,7 +4175,7 @@
         <v>129417981</v>
       </c>
       <c r="B29" t="n">
-        <v>91761</v>
+        <v>91766</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>129417982</v>
       </c>
       <c r="B30" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4408,7 +4408,7 @@
         <v>129417965</v>
       </c>
       <c r="B31" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4512,10 +4512,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129417987</v>
+        <v>129417985</v>
       </c>
       <c r="B32" t="n">
-        <v>92870</v>
+        <v>92875</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4547,10 +4547,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>367319</v>
+        <v>367272</v>
       </c>
       <c r="R32" t="n">
-        <v>6872675</v>
+        <v>6872689</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4582,7 +4582,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4619,10 +4619,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129417985</v>
+        <v>129417987</v>
       </c>
       <c r="B33" t="n">
-        <v>92870</v>
+        <v>92875</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4654,10 +4654,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>367272</v>
+        <v>367319</v>
       </c>
       <c r="R33" t="n">
-        <v>6872689</v>
+        <v>6872675</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4689,7 +4689,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4729,7 +4729,7 @@
         <v>129417967</v>
       </c>
       <c r="B34" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4833,32 +4833,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129417992</v>
+        <v>129417980</v>
       </c>
       <c r="B35" t="n">
-        <v>92870</v>
+        <v>91607</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>1204</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4868,10 +4868,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>367466</v>
+        <v>367486</v>
       </c>
       <c r="R35" t="n">
-        <v>6872692</v>
+        <v>6872703</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4913,7 +4913,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4940,32 +4940,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129417980</v>
+        <v>129417992</v>
       </c>
       <c r="B36" t="n">
-        <v>91602</v>
+        <v>92875</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1204</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4975,10 +4975,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>367486</v>
+        <v>367466</v>
       </c>
       <c r="R36" t="n">
-        <v>6872703</v>
+        <v>6872692</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5010,7 +5010,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5020,7 +5020,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5050,7 +5050,7 @@
         <v>129417978</v>
       </c>
       <c r="B37" t="n">
-        <v>78833</v>
+        <v>78838</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
         <v>129417993</v>
       </c>
       <c r="B39" t="n">
-        <v>92870</v>
+        <v>92875</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5371,7 +5371,7 @@
         <v>129417996</v>
       </c>
       <c r="B40" t="n">
-        <v>92870</v>
+        <v>92875</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5478,7 +5478,7 @@
         <v>129417984</v>
       </c>
       <c r="B41" t="n">
-        <v>92870</v>
+        <v>92875</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5585,7 +5585,7 @@
         <v>129417964</v>
       </c>
       <c r="B42" t="n">
-        <v>79108</v>
+        <v>79113</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         <v>129417995</v>
       </c>
       <c r="B43" t="n">
-        <v>92870</v>
+        <v>92875</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5799,7 +5799,7 @@
         <v>129417969</v>
       </c>
       <c r="B44" t="n">
-        <v>79666</v>
+        <v>79671</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5906,7 +5906,7 @@
         <v>129417997</v>
       </c>
       <c r="B45" t="n">
-        <v>92870</v>
+        <v>92875</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>129417991</v>
       </c>
       <c r="B46" t="n">
-        <v>92870</v>
+        <v>92875</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6117,10 +6117,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129417989</v>
+        <v>129417999</v>
       </c>
       <c r="B47" t="n">
-        <v>92870</v>
+        <v>92875</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6152,10 +6152,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>367400</v>
+        <v>367326</v>
       </c>
       <c r="R47" t="n">
-        <v>6872675</v>
+        <v>6872818</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6197,7 +6197,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6224,10 +6224,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129417999</v>
+        <v>129417989</v>
       </c>
       <c r="B48" t="n">
-        <v>92870</v>
+        <v>92875</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6259,10 +6259,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>367326</v>
+        <v>367400</v>
       </c>
       <c r="R48" t="n">
-        <v>6872818</v>
+        <v>6872675</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6304,7 +6304,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6334,7 +6334,7 @@
         <v>129417971</v>
       </c>
       <c r="B49" t="n">
-        <v>90620</v>
+        <v>90625</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6438,32 +6438,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129417998</v>
+        <v>129418002</v>
       </c>
       <c r="B50" t="n">
-        <v>92870</v>
+        <v>92869</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6473,10 +6473,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>367408</v>
+        <v>367263</v>
       </c>
       <c r="R50" t="n">
-        <v>6872746</v>
+        <v>6872692</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6508,7 +6508,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6518,7 +6518,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6545,32 +6545,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129418002</v>
+        <v>129417998</v>
       </c>
       <c r="B51" t="n">
-        <v>92864</v>
+        <v>92875</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6580,10 +6580,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>367263</v>
+        <v>367408</v>
       </c>
       <c r="R51" t="n">
-        <v>6872692</v>
+        <v>6872746</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6615,7 +6615,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6625,7 +6625,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6655,7 +6655,7 @@
         <v>129418003</v>
       </c>
       <c r="B52" t="n">
-        <v>78479</v>
+        <v>78484</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6762,7 +6762,7 @@
         <v>129418004</v>
       </c>
       <c r="B53" t="n">
-        <v>78479</v>
+        <v>78484</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6869,7 +6869,7 @@
         <v>129417990</v>
       </c>
       <c r="B54" t="n">
-        <v>92870</v>
+        <v>92875</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6976,7 +6976,7 @@
         <v>129417968</v>
       </c>
       <c r="B55" t="n">
-        <v>79666</v>
+        <v>79671</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7083,7 +7083,7 @@
         <v>129417994</v>
       </c>
       <c r="B56" t="n">
-        <v>92870</v>
+        <v>92875</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7190,7 +7190,7 @@
         <v>129418001</v>
       </c>
       <c r="B57" t="n">
-        <v>78084</v>
+        <v>78089</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 49122-2025 artfynd.xlsx
+++ b/artfynd/A 49122-2025 artfynd.xlsx
@@ -3288,10 +3288,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129417970</v>
+        <v>129417966</v>
       </c>
       <c r="B21" t="n">
-        <v>79671</v>
+        <v>79700</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3299,21 +3299,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3323,10 +3323,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>367279</v>
+        <v>367358</v>
       </c>
       <c r="R21" t="n">
-        <v>6872915</v>
+        <v>6872812</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3502,10 +3502,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129417966</v>
+        <v>129417970</v>
       </c>
       <c r="B23" t="n">
-        <v>79700</v>
+        <v>79671</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3513,21 +3513,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3537,10 +3537,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>367358</v>
+        <v>367279</v>
       </c>
       <c r="R23" t="n">
-        <v>6872812</v>
+        <v>6872915</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3572,7 +3572,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3582,7 +3582,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3609,57 +3609,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129417977</v>
+        <v>129417983</v>
       </c>
       <c r="B24" t="n">
-        <v>57840</v>
+        <v>79081</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Frönberget, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>367390</v>
+        <v>367341</v>
       </c>
       <c r="R24" t="n">
-        <v>6872907</v>
+        <v>6872850</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3691,7 +3679,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3701,7 +3689,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3710,8 +3698,24 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3728,7 +3732,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129417986</v>
+        <v>129417988</v>
       </c>
       <c r="B25" t="n">
         <v>92875</v>
@@ -3763,10 +3767,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>367310</v>
+        <v>367381</v>
       </c>
       <c r="R25" t="n">
-        <v>6872693</v>
+        <v>6872742</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3798,7 +3802,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3808,7 +3812,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3835,45 +3839,57 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129417975</v>
+        <v>129417977</v>
       </c>
       <c r="B26" t="n">
-        <v>92879</v>
+        <v>57840</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4365</v>
+        <v>103031</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Frönberget, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>367263</v>
+        <v>367390</v>
       </c>
       <c r="R26" t="n">
-        <v>6872692</v>
+        <v>6872907</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3905,7 +3921,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3915,7 +3931,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3942,7 +3958,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129417988</v>
+        <v>129417986</v>
       </c>
       <c r="B27" t="n">
         <v>92875</v>
@@ -3977,10 +3993,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>367381</v>
+        <v>367310</v>
       </c>
       <c r="R27" t="n">
-        <v>6872742</v>
+        <v>6872693</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4012,7 +4028,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4022,7 +4038,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4049,32 +4065,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129417983</v>
+        <v>129417975</v>
       </c>
       <c r="B28" t="n">
-        <v>79081</v>
+        <v>92879</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>4365</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -4084,10 +4100,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>367341</v>
+        <v>367263</v>
       </c>
       <c r="R28" t="n">
-        <v>6872850</v>
+        <v>6872692</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4119,7 +4135,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4129,7 +4145,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4138,24 +4154,8 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -5047,10 +5047,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129417978</v>
+        <v>129417976</v>
       </c>
       <c r="B37" t="n">
-        <v>78838</v>
+        <v>5493</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5058,21 +5058,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>101410</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>367466</v>
+        <v>367265</v>
       </c>
       <c r="R37" t="n">
-        <v>6872704</v>
+        <v>6872697</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5117,7 +5117,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5127,7 +5127,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5154,10 +5154,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129417976</v>
+        <v>129417978</v>
       </c>
       <c r="B38" t="n">
-        <v>5493</v>
+        <v>78838</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5165,21 +5165,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>101410</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5189,10 +5189,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>367265</v>
+        <v>367466</v>
       </c>
       <c r="R38" t="n">
-        <v>6872697</v>
+        <v>6872704</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5224,7 +5224,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5234,7 +5234,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -6759,32 +6759,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129418004</v>
+        <v>129417990</v>
       </c>
       <c r="B53" t="n">
-        <v>78484</v>
+        <v>92875</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6794,10 +6794,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>367380</v>
+        <v>367419</v>
       </c>
       <c r="R53" t="n">
-        <v>6872914</v>
+        <v>6872666</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6829,7 +6829,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6839,7 +6839,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6866,32 +6866,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129417990</v>
+        <v>129418004</v>
       </c>
       <c r="B54" t="n">
-        <v>92875</v>
+        <v>78484</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6901,10 +6901,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>367419</v>
+        <v>367380</v>
       </c>
       <c r="R54" t="n">
-        <v>6872666</v>
+        <v>6872914</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6946,7 +6946,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7187,10 +7187,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129418001</v>
+        <v>129417972</v>
       </c>
       <c r="B57" t="n">
-        <v>78089</v>
+        <v>57896</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7198,34 +7198,42 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6487</v>
+        <v>103021</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Frönberget, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>367471</v>
+        <v>367434</v>
       </c>
       <c r="R57" t="n">
-        <v>6872691</v>
+        <v>6872745</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7257,7 +7265,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7267,7 +7275,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7294,10 +7302,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129417972</v>
+        <v>129418001</v>
       </c>
       <c r="B58" t="n">
-        <v>57896</v>
+        <v>78089</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7305,42 +7313,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103021</v>
+        <v>6487</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Frönberget, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>367434</v>
+        <v>367471</v>
       </c>
       <c r="R58" t="n">
-        <v>6872745</v>
+        <v>6872691</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7372,7 +7372,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7382,7 +7382,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD58" t="b">

--- a/artfynd/A 49122-2025 artfynd.xlsx
+++ b/artfynd/A 49122-2025 artfynd.xlsx
@@ -3288,32 +3288,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129417966</v>
+        <v>129418000</v>
       </c>
       <c r="B21" t="n">
-        <v>79700</v>
+        <v>92875</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3323,10 +3323,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>367358</v>
+        <v>367377</v>
       </c>
       <c r="R21" t="n">
-        <v>6872812</v>
+        <v>6872921</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3395,32 +3395,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129418000</v>
+        <v>129417966</v>
       </c>
       <c r="B22" t="n">
-        <v>92875</v>
+        <v>79700</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3430,10 +3430,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>367377</v>
+        <v>367358</v>
       </c>
       <c r="R22" t="n">
-        <v>6872921</v>
+        <v>6872812</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3609,32 +3609,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129417983</v>
+        <v>129417988</v>
       </c>
       <c r="B24" t="n">
-        <v>79081</v>
+        <v>92875</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3644,10 +3644,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>367341</v>
+        <v>367381</v>
       </c>
       <c r="R24" t="n">
-        <v>6872850</v>
+        <v>6872742</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3679,7 +3679,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3689,7 +3689,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3698,24 +3698,8 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3732,32 +3716,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129417988</v>
+        <v>129417975</v>
       </c>
       <c r="B25" t="n">
-        <v>92875</v>
+        <v>92879</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3767,10 +3751,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>367381</v>
+        <v>367263</v>
       </c>
       <c r="R25" t="n">
-        <v>6872742</v>
+        <v>6872692</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3802,7 +3786,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3812,7 +3796,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3839,10 +3823,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129417977</v>
+        <v>129417986</v>
       </c>
       <c r="B26" t="n">
-        <v>57840</v>
+        <v>92875</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3850,46 +3834,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103031</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Frönberget, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>367390</v>
+        <v>367310</v>
       </c>
       <c r="R26" t="n">
-        <v>6872907</v>
+        <v>6872693</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3921,7 +3893,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3931,7 +3903,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3958,32 +3930,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129417986</v>
+        <v>129417983</v>
       </c>
       <c r="B27" t="n">
-        <v>92875</v>
+        <v>79081</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3993,10 +3965,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>367310</v>
+        <v>367341</v>
       </c>
       <c r="R27" t="n">
-        <v>6872693</v>
+        <v>6872850</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4028,7 +4000,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4038,7 +4010,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4047,8 +4019,24 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -4065,45 +4053,57 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129417975</v>
+        <v>129417977</v>
       </c>
       <c r="B28" t="n">
-        <v>92879</v>
+        <v>57840</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4365</v>
+        <v>103031</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Frönberget, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>367263</v>
+        <v>367390</v>
       </c>
       <c r="R28" t="n">
-        <v>6872692</v>
+        <v>6872907</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4135,7 +4135,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4833,32 +4833,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129417980</v>
+        <v>129417992</v>
       </c>
       <c r="B35" t="n">
-        <v>91607</v>
+        <v>92875</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1204</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4868,10 +4868,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>367486</v>
+        <v>367466</v>
       </c>
       <c r="R35" t="n">
-        <v>6872703</v>
+        <v>6872692</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4913,7 +4913,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4940,32 +4940,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129417992</v>
+        <v>129417980</v>
       </c>
       <c r="B36" t="n">
-        <v>92875</v>
+        <v>91607</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>1204</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4975,10 +4975,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>367466</v>
+        <v>367486</v>
       </c>
       <c r="R36" t="n">
-        <v>6872692</v>
+        <v>6872703</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5010,7 +5010,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5020,7 +5020,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5047,10 +5047,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129417976</v>
+        <v>129417978</v>
       </c>
       <c r="B37" t="n">
-        <v>5493</v>
+        <v>78838</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5058,21 +5058,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>101410</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>367265</v>
+        <v>367466</v>
       </c>
       <c r="R37" t="n">
-        <v>6872697</v>
+        <v>6872704</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5117,7 +5117,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5127,7 +5127,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5154,10 +5154,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129417978</v>
+        <v>129417976</v>
       </c>
       <c r="B38" t="n">
-        <v>78838</v>
+        <v>5493</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5165,21 +5165,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>101410</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5189,10 +5189,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>367466</v>
+        <v>367265</v>
       </c>
       <c r="R38" t="n">
-        <v>6872704</v>
+        <v>6872697</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5224,7 +5224,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5234,7 +5234,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5261,7 +5261,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129417993</v>
+        <v>129417984</v>
       </c>
       <c r="B39" t="n">
         <v>92875</v>
@@ -5296,10 +5296,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>367508</v>
+        <v>367266</v>
       </c>
       <c r="R39" t="n">
-        <v>6872697</v>
+        <v>6872707</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5331,7 +5331,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5341,7 +5341,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5475,7 +5475,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129417984</v>
+        <v>129417993</v>
       </c>
       <c r="B41" t="n">
         <v>92875</v>
@@ -5510,10 +5510,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>367266</v>
+        <v>367508</v>
       </c>
       <c r="R41" t="n">
-        <v>6872707</v>
+        <v>6872697</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5545,7 +5545,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5903,7 +5903,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129417997</v>
+        <v>129417989</v>
       </c>
       <c r="B45" t="n">
         <v>92875</v>
@@ -5938,10 +5938,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>367429</v>
+        <v>367400</v>
       </c>
       <c r="R45" t="n">
-        <v>6872754</v>
+        <v>6872675</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6010,7 +6010,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129417991</v>
+        <v>129417999</v>
       </c>
       <c r="B46" t="n">
         <v>92875</v>
@@ -6045,10 +6045,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>367457</v>
+        <v>367326</v>
       </c>
       <c r="R46" t="n">
-        <v>6872685</v>
+        <v>6872818</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6080,7 +6080,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6090,7 +6090,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6117,7 +6117,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129417999</v>
+        <v>129417991</v>
       </c>
       <c r="B47" t="n">
         <v>92875</v>
@@ -6152,10 +6152,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>367326</v>
+        <v>367457</v>
       </c>
       <c r="R47" t="n">
-        <v>6872818</v>
+        <v>6872685</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6197,7 +6197,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6224,7 +6224,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129417989</v>
+        <v>129417997</v>
       </c>
       <c r="B48" t="n">
         <v>92875</v>
@@ -6259,10 +6259,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>367400</v>
+        <v>367429</v>
       </c>
       <c r="R48" t="n">
-        <v>6872675</v>
+        <v>6872754</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6304,7 +6304,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6331,10 +6331,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129417971</v>
+        <v>129418002</v>
       </c>
       <c r="B49" t="n">
-        <v>90625</v>
+        <v>92869</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6342,21 +6342,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1962</v>
+        <v>4362</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6366,10 +6366,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>367385</v>
+        <v>367263</v>
       </c>
       <c r="R49" t="n">
-        <v>6872892</v>
+        <v>6872692</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6401,7 +6401,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6438,32 +6438,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129418002</v>
+        <v>129417998</v>
       </c>
       <c r="B50" t="n">
-        <v>92869</v>
+        <v>92875</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6473,10 +6473,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>367263</v>
+        <v>367408</v>
       </c>
       <c r="R50" t="n">
-        <v>6872692</v>
+        <v>6872746</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6508,7 +6508,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6518,7 +6518,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6545,32 +6545,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129417998</v>
+        <v>129417971</v>
       </c>
       <c r="B51" t="n">
-        <v>92875</v>
+        <v>90625</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6580,10 +6580,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>367408</v>
+        <v>367385</v>
       </c>
       <c r="R51" t="n">
-        <v>6872746</v>
+        <v>6872892</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6615,7 +6615,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6625,7 +6625,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6973,32 +6973,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129417968</v>
+        <v>129417994</v>
       </c>
       <c r="B55" t="n">
-        <v>79671</v>
+        <v>92875</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -7008,10 +7008,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>367311</v>
+        <v>367525</v>
       </c>
       <c r="R55" t="n">
-        <v>6872696</v>
+        <v>6872692</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7053,7 +7053,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7080,32 +7080,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129417994</v>
+        <v>129417968</v>
       </c>
       <c r="B56" t="n">
-        <v>92875</v>
+        <v>79671</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7115,10 +7115,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>367525</v>
+        <v>367311</v>
       </c>
       <c r="R56" t="n">
-        <v>6872692</v>
+        <v>6872696</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7150,7 +7150,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7160,7 +7160,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7187,10 +7187,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129417972</v>
+        <v>129418001</v>
       </c>
       <c r="B57" t="n">
-        <v>57896</v>
+        <v>78089</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7198,42 +7198,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103021</v>
+        <v>6487</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Frönberget, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>367434</v>
+        <v>367471</v>
       </c>
       <c r="R57" t="n">
-        <v>6872745</v>
+        <v>6872691</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7265,7 +7257,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7275,7 +7267,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7302,10 +7294,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129418001</v>
+        <v>129417972</v>
       </c>
       <c r="B58" t="n">
-        <v>78089</v>
+        <v>57896</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7313,34 +7305,42 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6487</v>
+        <v>103021</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Frönberget, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>367471</v>
+        <v>367434</v>
       </c>
       <c r="R58" t="n">
-        <v>6872691</v>
+        <v>6872745</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7372,7 +7372,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7382,7 +7382,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD58" t="b">

--- a/artfynd/A 49122-2025 artfynd.xlsx
+++ b/artfynd/A 49122-2025 artfynd.xlsx
@@ -3288,32 +3288,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129418000</v>
+        <v>129417966</v>
       </c>
       <c r="B21" t="n">
-        <v>92875</v>
+        <v>79700</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3323,10 +3323,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>367377</v>
+        <v>367358</v>
       </c>
       <c r="R21" t="n">
-        <v>6872921</v>
+        <v>6872812</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3395,32 +3395,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129417966</v>
+        <v>129418000</v>
       </c>
       <c r="B22" t="n">
-        <v>79700</v>
+        <v>92875</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3430,10 +3430,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>367358</v>
+        <v>367377</v>
       </c>
       <c r="R22" t="n">
-        <v>6872812</v>
+        <v>6872921</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3609,7 +3609,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129417988</v>
+        <v>129417986</v>
       </c>
       <c r="B24" t="n">
         <v>92875</v>
@@ -3644,10 +3644,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>367381</v>
+        <v>367310</v>
       </c>
       <c r="R24" t="n">
-        <v>6872742</v>
+        <v>6872693</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3679,7 +3679,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3689,7 +3689,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3716,32 +3716,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129417975</v>
+        <v>129417988</v>
       </c>
       <c r="B25" t="n">
-        <v>92879</v>
+        <v>92875</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3751,10 +3751,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>367263</v>
+        <v>367381</v>
       </c>
       <c r="R25" t="n">
-        <v>6872692</v>
+        <v>6872742</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3796,7 +3796,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3823,32 +3823,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129417986</v>
+        <v>129417983</v>
       </c>
       <c r="B26" t="n">
-        <v>92875</v>
+        <v>79081</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3858,10 +3858,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>367310</v>
+        <v>367341</v>
       </c>
       <c r="R26" t="n">
-        <v>6872693</v>
+        <v>6872850</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3893,7 +3893,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3903,7 +3903,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3912,8 +3912,24 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3930,32 +3946,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129417983</v>
+        <v>129417975</v>
       </c>
       <c r="B27" t="n">
-        <v>79081</v>
+        <v>92879</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>4365</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3965,10 +3981,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>367341</v>
+        <v>367263</v>
       </c>
       <c r="R27" t="n">
-        <v>6872850</v>
+        <v>6872692</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4000,7 +4016,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4010,7 +4026,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4019,24 +4035,8 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -4172,45 +4172,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129417981</v>
+        <v>129417982</v>
       </c>
       <c r="B29" t="n">
-        <v>91766</v>
+        <v>79081</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Frönberget, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>367358</v>
+        <v>367313</v>
       </c>
       <c r="R29" t="n">
-        <v>6872748</v>
+        <v>6872755</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4242,7 +4245,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4252,7 +4255,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4261,8 +4264,24 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -4279,10 +4298,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129417982</v>
+        <v>129417965</v>
       </c>
       <c r="B30" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4290,37 +4309,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Frönberget, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>367313</v>
+        <v>367465</v>
       </c>
       <c r="R30" t="n">
-        <v>6872755</v>
+        <v>6872703</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4352,7 +4368,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4362,7 +4378,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4371,24 +4387,8 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4405,32 +4405,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129417965</v>
+        <v>129417981</v>
       </c>
       <c r="B31" t="n">
-        <v>79700</v>
+        <v>91766</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>1503</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4440,10 +4440,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>367465</v>
+        <v>367358</v>
       </c>
       <c r="R31" t="n">
-        <v>6872703</v>
+        <v>6872748</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4833,32 +4833,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129417992</v>
+        <v>129417980</v>
       </c>
       <c r="B35" t="n">
-        <v>92875</v>
+        <v>91607</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>1204</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4868,10 +4868,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>367466</v>
+        <v>367486</v>
       </c>
       <c r="R35" t="n">
-        <v>6872692</v>
+        <v>6872703</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4913,7 +4913,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4940,32 +4940,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129417980</v>
+        <v>129417992</v>
       </c>
       <c r="B36" t="n">
-        <v>91607</v>
+        <v>92875</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1204</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4975,10 +4975,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>367486</v>
+        <v>367466</v>
       </c>
       <c r="R36" t="n">
-        <v>6872703</v>
+        <v>6872692</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5010,7 +5010,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5020,7 +5020,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5261,7 +5261,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129417984</v>
+        <v>129417993</v>
       </c>
       <c r="B39" t="n">
         <v>92875</v>
@@ -5296,10 +5296,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>367266</v>
+        <v>367508</v>
       </c>
       <c r="R39" t="n">
-        <v>6872707</v>
+        <v>6872697</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5331,7 +5331,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5341,7 +5341,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5475,7 +5475,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129417993</v>
+        <v>129417984</v>
       </c>
       <c r="B41" t="n">
         <v>92875</v>
@@ -5510,10 +5510,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>367508</v>
+        <v>367266</v>
       </c>
       <c r="R41" t="n">
-        <v>6872697</v>
+        <v>6872707</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5545,7 +5545,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5903,7 +5903,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129417989</v>
+        <v>129417991</v>
       </c>
       <c r="B45" t="n">
         <v>92875</v>
@@ -5938,10 +5938,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>367400</v>
+        <v>367457</v>
       </c>
       <c r="R45" t="n">
-        <v>6872675</v>
+        <v>6872685</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6010,7 +6010,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129417999</v>
+        <v>129417997</v>
       </c>
       <c r="B46" t="n">
         <v>92875</v>
@@ -6045,10 +6045,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>367326</v>
+        <v>367429</v>
       </c>
       <c r="R46" t="n">
-        <v>6872818</v>
+        <v>6872754</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6080,7 +6080,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6090,7 +6090,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6117,7 +6117,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129417991</v>
+        <v>129417999</v>
       </c>
       <c r="B47" t="n">
         <v>92875</v>
@@ -6152,10 +6152,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>367457</v>
+        <v>367326</v>
       </c>
       <c r="R47" t="n">
-        <v>6872685</v>
+        <v>6872818</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6197,7 +6197,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6224,7 +6224,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129417997</v>
+        <v>129417989</v>
       </c>
       <c r="B48" t="n">
         <v>92875</v>
@@ -6259,10 +6259,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>367429</v>
+        <v>367400</v>
       </c>
       <c r="R48" t="n">
-        <v>6872754</v>
+        <v>6872675</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6304,7 +6304,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6331,10 +6331,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129418002</v>
+        <v>129417971</v>
       </c>
       <c r="B49" t="n">
-        <v>92869</v>
+        <v>90625</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6342,21 +6342,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4362</v>
+        <v>1962</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6366,10 +6366,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>367263</v>
+        <v>367385</v>
       </c>
       <c r="R49" t="n">
-        <v>6872692</v>
+        <v>6872892</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6401,7 +6401,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6438,32 +6438,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129417998</v>
+        <v>129418002</v>
       </c>
       <c r="B50" t="n">
-        <v>92875</v>
+        <v>92869</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6473,10 +6473,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>367408</v>
+        <v>367263</v>
       </c>
       <c r="R50" t="n">
-        <v>6872746</v>
+        <v>6872692</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6508,7 +6508,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6518,7 +6518,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6545,32 +6545,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129417971</v>
+        <v>129417998</v>
       </c>
       <c r="B51" t="n">
-        <v>90625</v>
+        <v>92875</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6580,10 +6580,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>367385</v>
+        <v>367408</v>
       </c>
       <c r="R51" t="n">
-        <v>6872892</v>
+        <v>6872746</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6615,7 +6615,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6625,7 +6625,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD51" t="b">

--- a/artfynd/A 49122-2025 artfynd.xlsx
+++ b/artfynd/A 49122-2025 artfynd.xlsx
@@ -3288,32 +3288,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129417966</v>
+        <v>129418000</v>
       </c>
       <c r="B21" t="n">
-        <v>79700</v>
+        <v>92879</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3323,10 +3323,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>367358</v>
+        <v>367377</v>
       </c>
       <c r="R21" t="n">
-        <v>6872812</v>
+        <v>6872921</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3395,32 +3395,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129418000</v>
+        <v>129417966</v>
       </c>
       <c r="B22" t="n">
-        <v>92875</v>
+        <v>79700</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3430,10 +3430,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>367377</v>
+        <v>367358</v>
       </c>
       <c r="R22" t="n">
-        <v>6872921</v>
+        <v>6872812</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3612,7 +3612,7 @@
         <v>129417986</v>
       </c>
       <c r="B24" t="n">
-        <v>92875</v>
+        <v>92879</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3716,32 +3716,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129417988</v>
+        <v>129417975</v>
       </c>
       <c r="B25" t="n">
-        <v>92875</v>
+        <v>92883</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3751,10 +3751,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>367381</v>
+        <v>367263</v>
       </c>
       <c r="R25" t="n">
-        <v>6872742</v>
+        <v>6872692</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3796,7 +3796,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3823,32 +3823,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129417983</v>
+        <v>129417988</v>
       </c>
       <c r="B26" t="n">
-        <v>79081</v>
+        <v>92879</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3858,10 +3858,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>367341</v>
+        <v>367381</v>
       </c>
       <c r="R26" t="n">
-        <v>6872850</v>
+        <v>6872742</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3893,7 +3893,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3903,7 +3903,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3912,24 +3912,8 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3946,45 +3930,57 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129417975</v>
+        <v>129417977</v>
       </c>
       <c r="B27" t="n">
-        <v>92879</v>
+        <v>57840</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4365</v>
+        <v>103031</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Frönberget, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>367263</v>
+        <v>367390</v>
       </c>
       <c r="R27" t="n">
-        <v>6872692</v>
+        <v>6872907</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4016,7 +4012,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4026,7 +4022,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4053,57 +4049,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129417977</v>
+        <v>129417983</v>
       </c>
       <c r="B28" t="n">
-        <v>57840</v>
+        <v>79081</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Frönberget, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>367390</v>
+        <v>367341</v>
       </c>
       <c r="R28" t="n">
-        <v>6872907</v>
+        <v>6872850</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4135,7 +4119,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4145,7 +4129,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4154,8 +4138,24 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -4172,48 +4172,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129417982</v>
+        <v>129417981</v>
       </c>
       <c r="B29" t="n">
-        <v>79081</v>
+        <v>91770</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Frönberget, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>367313</v>
+        <v>367358</v>
       </c>
       <c r="R29" t="n">
-        <v>6872755</v>
+        <v>6872748</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4245,7 +4242,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4255,7 +4252,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4264,24 +4261,8 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -4298,10 +4279,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129417965</v>
+        <v>129417982</v>
       </c>
       <c r="B30" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4309,34 +4290,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Frönberget, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>367465</v>
+        <v>367313</v>
       </c>
       <c r="R30" t="n">
-        <v>6872703</v>
+        <v>6872755</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4368,7 +4352,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4378,7 +4362,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4387,8 +4371,24 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4405,32 +4405,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129417981</v>
+        <v>129417965</v>
       </c>
       <c r="B31" t="n">
-        <v>91766</v>
+        <v>79700</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4440,10 +4440,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>367358</v>
+        <v>367465</v>
       </c>
       <c r="R31" t="n">
-        <v>6872748</v>
+        <v>6872703</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4515,7 +4515,7 @@
         <v>129417985</v>
       </c>
       <c r="B32" t="n">
-        <v>92875</v>
+        <v>92879</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4622,7 +4622,7 @@
         <v>129417987</v>
       </c>
       <c r="B33" t="n">
-        <v>92875</v>
+        <v>92879</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4836,7 +4836,7 @@
         <v>129417980</v>
       </c>
       <c r="B35" t="n">
-        <v>91607</v>
+        <v>91611</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4943,7 +4943,7 @@
         <v>129417992</v>
       </c>
       <c r="B36" t="n">
-        <v>92875</v>
+        <v>92879</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
         <v>129417993</v>
       </c>
       <c r="B39" t="n">
-        <v>92875</v>
+        <v>92879</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5371,7 +5371,7 @@
         <v>129417996</v>
       </c>
       <c r="B40" t="n">
-        <v>92875</v>
+        <v>92879</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5478,7 +5478,7 @@
         <v>129417984</v>
       </c>
       <c r="B41" t="n">
-        <v>92875</v>
+        <v>92879</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         <v>129417995</v>
       </c>
       <c r="B43" t="n">
-        <v>92875</v>
+        <v>92879</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5903,10 +5903,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129417991</v>
+        <v>129417997</v>
       </c>
       <c r="B45" t="n">
-        <v>92875</v>
+        <v>92879</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5938,10 +5938,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>367457</v>
+        <v>367429</v>
       </c>
       <c r="R45" t="n">
-        <v>6872685</v>
+        <v>6872754</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6010,10 +6010,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129417997</v>
+        <v>129417991</v>
       </c>
       <c r="B46" t="n">
-        <v>92875</v>
+        <v>92879</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6045,10 +6045,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>367429</v>
+        <v>367457</v>
       </c>
       <c r="R46" t="n">
-        <v>6872754</v>
+        <v>6872685</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6080,7 +6080,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6090,7 +6090,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6120,7 +6120,7 @@
         <v>129417999</v>
       </c>
       <c r="B47" t="n">
-        <v>92875</v>
+        <v>92879</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6227,7 +6227,7 @@
         <v>129417989</v>
       </c>
       <c r="B48" t="n">
-        <v>92875</v>
+        <v>92879</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6331,10 +6331,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129417971</v>
+        <v>129418002</v>
       </c>
       <c r="B49" t="n">
-        <v>90625</v>
+        <v>92873</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6342,21 +6342,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1962</v>
+        <v>4362</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6366,10 +6366,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>367385</v>
+        <v>367263</v>
       </c>
       <c r="R49" t="n">
-        <v>6872892</v>
+        <v>6872692</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6401,7 +6401,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6438,32 +6438,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129418002</v>
+        <v>129417998</v>
       </c>
       <c r="B50" t="n">
-        <v>92869</v>
+        <v>92879</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6473,10 +6473,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>367263</v>
+        <v>367408</v>
       </c>
       <c r="R50" t="n">
-        <v>6872692</v>
+        <v>6872746</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6508,7 +6508,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6518,7 +6518,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6545,32 +6545,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129417998</v>
+        <v>129417971</v>
       </c>
       <c r="B51" t="n">
-        <v>92875</v>
+        <v>90629</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6580,10 +6580,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>367408</v>
+        <v>367385</v>
       </c>
       <c r="R51" t="n">
-        <v>6872746</v>
+        <v>6872892</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6615,7 +6615,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6625,7 +6625,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6762,7 +6762,7 @@
         <v>129417990</v>
       </c>
       <c r="B53" t="n">
-        <v>92875</v>
+        <v>92879</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6976,7 +6976,7 @@
         <v>129417994</v>
       </c>
       <c r="B55" t="n">
-        <v>92875</v>
+        <v>92879</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 49122-2025 artfynd.xlsx
+++ b/artfynd/A 49122-2025 artfynd.xlsx
@@ -3291,7 +3291,7 @@
         <v>129418000</v>
       </c>
       <c r="B21" t="n">
-        <v>92879</v>
+        <v>92881</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3609,32 +3609,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129417986</v>
+        <v>129417983</v>
       </c>
       <c r="B24" t="n">
-        <v>92879</v>
+        <v>79081</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3644,10 +3644,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>367310</v>
+        <v>367341</v>
       </c>
       <c r="R24" t="n">
-        <v>6872693</v>
+        <v>6872850</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3679,7 +3679,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3689,7 +3689,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3698,8 +3698,24 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3716,32 +3732,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129417975</v>
+        <v>129417986</v>
       </c>
       <c r="B25" t="n">
-        <v>92883</v>
+        <v>92881</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3751,10 +3767,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>367263</v>
+        <v>367310</v>
       </c>
       <c r="R25" t="n">
-        <v>6872692</v>
+        <v>6872693</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3786,7 +3802,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3796,7 +3812,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3823,32 +3839,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129417988</v>
+        <v>129417975</v>
       </c>
       <c r="B26" t="n">
-        <v>92879</v>
+        <v>92885</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3858,10 +3874,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>367381</v>
+        <v>367263</v>
       </c>
       <c r="R26" t="n">
-        <v>6872742</v>
+        <v>6872692</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3893,7 +3909,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3903,7 +3919,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3930,10 +3946,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129417977</v>
+        <v>129417988</v>
       </c>
       <c r="B27" t="n">
-        <v>57840</v>
+        <v>92881</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3941,46 +3957,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103031</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Frönberget, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>367390</v>
+        <v>367381</v>
       </c>
       <c r="R27" t="n">
-        <v>6872907</v>
+        <v>6872742</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4012,7 +4016,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4022,7 +4026,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4049,45 +4053,57 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129417983</v>
+        <v>129417977</v>
       </c>
       <c r="B28" t="n">
-        <v>79081</v>
+        <v>57840</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Frönberget, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>367341</v>
+        <v>367390</v>
       </c>
       <c r="R28" t="n">
-        <v>6872850</v>
+        <v>6872907</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4119,7 +4135,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4129,7 +4145,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4138,24 +4154,8 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -4175,7 +4175,7 @@
         <v>129417981</v>
       </c>
       <c r="B29" t="n">
-        <v>91770</v>
+        <v>91772</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
         <v>129417985</v>
       </c>
       <c r="B32" t="n">
-        <v>92879</v>
+        <v>92881</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4622,7 +4622,7 @@
         <v>129417987</v>
       </c>
       <c r="B33" t="n">
-        <v>92879</v>
+        <v>92881</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4836,7 +4836,7 @@
         <v>129417980</v>
       </c>
       <c r="B35" t="n">
-        <v>91611</v>
+        <v>91613</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4943,7 +4943,7 @@
         <v>129417992</v>
       </c>
       <c r="B36" t="n">
-        <v>92879</v>
+        <v>92881</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
         <v>129417993</v>
       </c>
       <c r="B39" t="n">
-        <v>92879</v>
+        <v>92881</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5371,7 +5371,7 @@
         <v>129417996</v>
       </c>
       <c r="B40" t="n">
-        <v>92879</v>
+        <v>92881</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5478,7 +5478,7 @@
         <v>129417984</v>
       </c>
       <c r="B41" t="n">
-        <v>92879</v>
+        <v>92881</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         <v>129417995</v>
       </c>
       <c r="B43" t="n">
-        <v>92879</v>
+        <v>92881</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5906,7 +5906,7 @@
         <v>129417997</v>
       </c>
       <c r="B45" t="n">
-        <v>92879</v>
+        <v>92881</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>129417991</v>
       </c>
       <c r="B46" t="n">
-        <v>92879</v>
+        <v>92881</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
         <v>129417999</v>
       </c>
       <c r="B47" t="n">
-        <v>92879</v>
+        <v>92881</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6227,7 +6227,7 @@
         <v>129417989</v>
       </c>
       <c r="B48" t="n">
-        <v>92879</v>
+        <v>92881</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6331,10 +6331,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129418002</v>
+        <v>129417971</v>
       </c>
       <c r="B49" t="n">
-        <v>92873</v>
+        <v>90631</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6342,21 +6342,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4362</v>
+        <v>1962</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6366,10 +6366,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>367263</v>
+        <v>367385</v>
       </c>
       <c r="R49" t="n">
-        <v>6872692</v>
+        <v>6872892</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6401,7 +6401,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6438,32 +6438,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129417998</v>
+        <v>129418002</v>
       </c>
       <c r="B50" t="n">
-        <v>92879</v>
+        <v>92875</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6473,10 +6473,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>367408</v>
+        <v>367263</v>
       </c>
       <c r="R50" t="n">
-        <v>6872746</v>
+        <v>6872692</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6508,7 +6508,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6518,7 +6518,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6545,32 +6545,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129417971</v>
+        <v>129417998</v>
       </c>
       <c r="B51" t="n">
-        <v>90629</v>
+        <v>92881</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6580,10 +6580,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>367385</v>
+        <v>367408</v>
       </c>
       <c r="R51" t="n">
-        <v>6872892</v>
+        <v>6872746</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6615,7 +6615,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6625,7 +6625,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6762,7 +6762,7 @@
         <v>129417990</v>
       </c>
       <c r="B53" t="n">
-        <v>92879</v>
+        <v>92881</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6976,7 +6976,7 @@
         <v>129417994</v>
       </c>
       <c r="B55" t="n">
-        <v>92879</v>
+        <v>92881</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 49122-2025 artfynd.xlsx
+++ b/artfynd/A 49122-2025 artfynd.xlsx
@@ -6973,32 +6973,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129417994</v>
+        <v>129417968</v>
       </c>
       <c r="B55" t="n">
-        <v>92881</v>
+        <v>79671</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -7008,10 +7008,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>367525</v>
+        <v>367311</v>
       </c>
       <c r="R55" t="n">
-        <v>6872692</v>
+        <v>6872696</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7053,7 +7053,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7080,32 +7080,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129417968</v>
+        <v>129417994</v>
       </c>
       <c r="B56" t="n">
-        <v>79671</v>
+        <v>92881</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7115,10 +7115,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>367311</v>
+        <v>367525</v>
       </c>
       <c r="R56" t="n">
-        <v>6872696</v>
+        <v>6872692</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7150,7 +7150,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7160,7 +7160,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD56" t="b">

--- a/artfynd/A 49122-2025 artfynd.xlsx
+++ b/artfynd/A 49122-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY60"/>
+  <dimension ref="A1:AZ60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129417964</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121149664</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -992,6 +1007,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129417980</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1099,6 +1119,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129417981</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1206,6 +1231,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129417971</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1351,6 +1381,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118773930</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1492,6 +1527,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121839011</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1633,6 +1673,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121839230</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1740,6 +1785,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129418002</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1846,6 +1896,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121149667</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1953,6 +2008,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129417984</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2060,6 +2120,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129417985</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2167,6 +2232,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129417986</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2274,6 +2344,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129417987</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2381,6 +2456,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129417988</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2488,6 +2568,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129417989</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2595,6 +2680,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129417990</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2702,6 +2792,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129417991</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2809,6 +2904,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129417992</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2916,6 +3016,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129417993</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3023,6 +3128,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129417994</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3130,6 +3240,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129417995</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3237,6 +3352,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129417996</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3344,6 +3464,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129417997</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3451,6 +3576,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129417998</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3558,6 +3688,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129417999</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3665,6 +3800,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129418000</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3772,6 +3912,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129417975</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3926,6 +4071,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121838873</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4051,6 +4201,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121870987</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4177,6 +4332,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129417982</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4300,6 +4460,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129417983</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4407,6 +4572,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129418003</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4514,6 +4684,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129418004</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4620,6 +4795,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121149666</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4727,6 +4907,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129417978</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4877,6 +5062,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121839141</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4984,6 +5174,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129417965</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5091,6 +5286,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129417966</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5198,6 +5398,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129417967</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5328,6 +5533,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118773153</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5469,6 +5679,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121838983</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5576,6 +5791,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129418001</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5706,6 +5926,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121836311</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5831,6 +6056,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121838789</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5961,6 +6191,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121839048</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6103,6 +6338,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121871040</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6210,6 +6450,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129417976</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6344,6 +6589,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121838469</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6459,6 +6709,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129417972</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6578,6 +6833,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129417977</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6723,6 +6983,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118773698</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6869,6 +7134,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121837740</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6975,6 +7245,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121149665</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7082,6 +7357,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129417968</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7189,6 +7469,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129417969</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7296,6 +7581,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129417970</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7403,6 +7693,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129417973</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7510,8 +7805,74 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129417974</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>